--- a/Bom.xlsx
+++ b/Bom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Victus\Desktop\AVIONIX-28\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D053CBEC-816D-4871-BBE7-2E6E1836C38D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFAD2B1-F885-4AD6-BAF2-18C77F43D4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="1452" windowWidth="21600" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>xxxx xxxx xxxxx xxPCS BOM  (Sample Bill of Materials)</t>
   </si>
@@ -127,12 +127,6 @@
   </si>
   <si>
     <t>thru-hole</t>
-  </si>
-  <si>
-    <t>Need a quick and accurante quote? Need an efficient production? Please read SMT Ordering Necessary Files &amp; Info in 1 minute. Thank you very much!</t>
-  </si>
-  <si>
-    <t>Click for Instructions on How to Create a BOM</t>
   </si>
   <si>
     <t>J1,J2,J3,J4</t>
@@ -823,21 +817,23 @@
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6"/>
+      <c r="A7" s="6">
+        <v>1</v>
+      </c>
       <c r="B7" s="7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" s="6">
         <v>4</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="17" t="s">
@@ -846,9 +842,11 @@
       <c r="I7" s="9"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6"/>
+      <c r="A8" s="6">
+        <v>2</v>
+      </c>
       <c r="B8" s="19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C8" s="20">
         <v>1</v>
@@ -856,16 +854,18 @@
       <c r="D8" s="21"/>
       <c r="E8" s="22"/>
       <c r="F8" s="23" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="25"/>
       <c r="I8" s="26"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6"/>
+      <c r="A9" s="6">
+        <v>3</v>
+      </c>
       <c r="B9" s="19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" s="20">
         <v>1</v>
@@ -873,16 +873,18 @@
       <c r="D9" s="21"/>
       <c r="E9" s="21"/>
       <c r="F9" s="23" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G9" s="22"/>
       <c r="H9" s="27"/>
       <c r="I9" s="27"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6"/>
+      <c r="A10" s="6">
+        <v>4</v>
+      </c>
       <c r="B10" s="19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10" s="20">
         <v>1</v>
@@ -890,16 +892,18 @@
       <c r="D10" s="21"/>
       <c r="E10" s="21"/>
       <c r="F10" s="23" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G10" s="22"/>
       <c r="H10" s="27"/>
       <c r="I10" s="27"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6"/>
+      <c r="A11" s="6">
+        <v>5</v>
+      </c>
       <c r="B11" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C11" s="20">
         <v>1</v>
@@ -907,16 +911,18 @@
       <c r="D11" s="21"/>
       <c r="E11" s="21"/>
       <c r="F11" s="23" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G11" s="22"/>
       <c r="H11" s="27"/>
       <c r="I11" s="27"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6"/>
+      <c r="A12" s="6">
+        <v>6</v>
+      </c>
       <c r="B12" s="19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C12" s="20">
         <v>1</v>
@@ -924,16 +930,18 @@
       <c r="D12" s="21"/>
       <c r="E12" s="21"/>
       <c r="F12" s="23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G12" s="28"/>
       <c r="H12" s="27"/>
       <c r="I12" s="27"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6"/>
+      <c r="A13" s="6">
+        <v>7</v>
+      </c>
       <c r="B13" s="19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C13" s="20">
         <v>1</v>
@@ -941,16 +949,18 @@
       <c r="D13" s="21"/>
       <c r="E13" s="21"/>
       <c r="F13" s="23" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G13" s="28"/>
       <c r="H13" s="27"/>
       <c r="I13" s="27"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6"/>
+      <c r="A14" s="6">
+        <v>8</v>
+      </c>
       <c r="B14" s="19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C14" s="20">
         <v>1</v>
@@ -958,16 +968,18 @@
       <c r="D14" s="21"/>
       <c r="E14" s="21"/>
       <c r="F14" s="19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G14" s="28"/>
       <c r="H14" s="27"/>
       <c r="I14" s="27"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6"/>
+      <c r="A15" s="6">
+        <v>9</v>
+      </c>
       <c r="B15" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C15" s="20">
         <v>1</v>
@@ -975,7 +987,7 @@
       <c r="D15" s="21"/>
       <c r="E15" s="21"/>
       <c r="F15" s="19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G15" s="28"/>
       <c r="H15" s="27"/>
@@ -1048,9 +1060,7 @@
       <c r="I21" s="9"/>
     </row>
     <row r="24" spans="1:9" ht="14.4">
-      <c r="A24" s="12" t="s">
-        <v>11</v>
-      </c>
+      <c r="A24" s="12"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -1072,9 +1082,7 @@
       <c r="I25" s="11"/>
     </row>
     <row r="26" spans="1:9" s="2" customFormat="1" ht="14.4">
-      <c r="A26" s="13" t="s">
-        <v>12</v>
-      </c>
+      <c r="A26" s="13"/>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -1091,14 +1099,9 @@
     <mergeCell ref="D2:F4"/>
     <mergeCell ref="A2:B3"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="A26" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A24" display="Need a quick and accurante quote? Need an efficient production? Please read SMT Ordering Necessary Files &amp; Info in 1 minute. Thank you very much!" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="A24:I24" r:id="rId2" display="Need a quick and accurante quote? Need an efficient production? Please read SMT Ordering Necessary Files &amp; Info in 1 minute. Thank you very much!" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-  </hyperlinks>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="300"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Bom.xlsx
+++ b/Bom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Victus\Desktop\AVIONIX-28\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFAD2B1-F885-4AD6-BAF2-18C77F43D4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A543CDD-6153-446E-AD73-5BC861E96107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="1452" windowWidth="21600" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>xxxx xxxx xxxxx xxPCS BOM  (Sample Bill of Materials)</t>
   </si>
@@ -184,6 +184,15 @@
   </si>
   <si>
     <t>10uF</t>
+  </si>
+  <si>
+    <t>smd</t>
+  </si>
+  <si>
+    <t>1206</t>
+  </si>
+  <si>
+    <t>0805</t>
   </si>
 </sst>
 </file>
@@ -262,7 +271,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -284,6 +293,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -321,7 +336,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -355,18 +370,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -398,6 +401,21 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -767,25 +785,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="19.5" customHeight="1">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="D2" s="14" t="s">
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
+      <c r="D2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="6" spans="1:9" ht="28.5" customHeight="1">
       <c r="A6" s="3" t="s">
@@ -829,14 +847,14 @@
       <c r="D7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="14" t="s">
         <v>28</v>
       </c>
       <c r="G7" s="8"/>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="13" t="s">
         <v>10</v>
       </c>
       <c r="I7" s="9"/>
@@ -845,164 +863,172 @@
       <c r="A8" s="6">
         <v>2</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="16">
         <v>1</v>
       </c>
-      <c r="D8" s="21"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="23" t="s">
+      <c r="D8" s="17"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="24"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="26"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6">
         <v>3</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="16">
         <v>1</v>
       </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="23" t="s">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="22"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6">
         <v>4</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="16">
         <v>1</v>
       </c>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="23" t="s">
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="22"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6">
         <v>5</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="16">
         <v>1</v>
       </c>
-      <c r="D11" s="21"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="23" t="s">
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="22"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6">
         <v>6</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="16">
         <v>1</v>
       </c>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="23" t="s">
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="28"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6">
         <v>7</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="16">
         <v>1</v>
       </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="23" t="s">
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G13" s="28"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
+      <c r="G13" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="23"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6">
         <v>8</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="16">
         <v>1</v>
       </c>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="19" t="s">
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="G14" s="28"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
+      <c r="G14" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="23"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6">
         <v>9</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="16">
         <v>1</v>
       </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="19" t="s">
+      <c r="D15" s="29"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="28"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
@@ -1060,15 +1086,15 @@
       <c r="I21" s="9"/>
     </row>
     <row r="24" spans="1:9" ht="14.4">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="12"/>
+      <c r="A24" s="25"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
     </row>
     <row r="25" spans="1:9" ht="14.4">
       <c r="A25" s="11"/>
@@ -1082,15 +1108,15 @@
       <c r="I25" s="11"/>
     </row>
     <row r="26" spans="1:9" s="2" customFormat="1" ht="14.4">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
+      <c r="A26" s="26"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Bom.xlsx
+++ b/Bom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Victus\Desktop\AVIONIX-28\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A543CDD-6153-446E-AD73-5BC861E96107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60E6DBA-76F3-439F-8223-3598ABF71483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24" yWindow="3396" windowWidth="21600" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
   <si>
     <t>xxxx xxxx xxxxx xxPCS BOM  (Sample Bill of Materials)</t>
   </si>
@@ -402,6 +402,9 @@
     <xf numFmtId="49" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -413,9 +416,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -785,25 +785,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="19.5" customHeight="1">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="D2" s="27" t="s">
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="D2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
     </row>
     <row r="6" spans="1:9" ht="28.5" customHeight="1">
       <c r="A6" s="3" t="s">
@@ -875,7 +875,9 @@
         <v>29</v>
       </c>
       <c r="G8" s="20"/>
-      <c r="H8" s="21"/>
+      <c r="H8" s="21" t="s">
+        <v>30</v>
+      </c>
       <c r="I8" s="22"/>
     </row>
     <row r="9" spans="1:9">
@@ -894,7 +896,9 @@
         <v>25</v>
       </c>
       <c r="G9" s="18"/>
-      <c r="H9" s="23"/>
+      <c r="H9" s="23" t="s">
+        <v>30</v>
+      </c>
       <c r="I9" s="23"/>
     </row>
     <row r="10" spans="1:9">
@@ -913,7 +917,9 @@
         <v>25</v>
       </c>
       <c r="G10" s="18"/>
-      <c r="H10" s="23"/>
+      <c r="H10" s="23" t="s">
+        <v>30</v>
+      </c>
       <c r="I10" s="23"/>
     </row>
     <row r="11" spans="1:9">
@@ -932,7 +938,9 @@
         <v>26</v>
       </c>
       <c r="G11" s="18"/>
-      <c r="H11" s="23"/>
+      <c r="H11" s="23" t="s">
+        <v>30</v>
+      </c>
       <c r="I11" s="23"/>
     </row>
     <row r="12" spans="1:9">
@@ -1010,7 +1018,7 @@
       <c r="C15" s="16">
         <v>1</v>
       </c>
-      <c r="D15" s="29"/>
+      <c r="D15" s="25"/>
       <c r="E15" s="17"/>
       <c r="F15" s="15" t="s">
         <v>24</v>
@@ -1086,15 +1094,15 @@
       <c r="I21" s="9"/>
     </row>
     <row r="24" spans="1:9" ht="14.4">
-      <c r="A24" s="25"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
+      <c r="A24" s="26"/>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
     </row>
     <row r="25" spans="1:9" ht="14.4">
       <c r="A25" s="11"/>
@@ -1108,15 +1116,15 @@
       <c r="I25" s="11"/>
     </row>
     <row r="26" spans="1:9" s="2" customFormat="1" ht="14.4">
-      <c r="A26" s="26"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
+      <c r="A26" s="27"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="27"/>
+      <c r="I26" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Bom.xlsx
+++ b/Bom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Victus\Desktop\AVIONIX-28\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60E6DBA-76F3-439F-8223-3598ABF71483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE09176-F67B-4660-AE46-AB46F2812886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24" yWindow="3396" windowWidth="21600" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="948" windowWidth="21600" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,10 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
-  <si>
-    <t>xxxx xxxx xxxxx xxPCS BOM  (Sample Bill of Materials)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>Item #</t>
   </si>
@@ -183,9 +180,6 @@
     <t>28v,5v,3.3v,1.8v rail input and output</t>
   </si>
   <si>
-    <t>10uF</t>
-  </si>
-  <si>
     <t>smd</t>
   </si>
   <si>
@@ -193,6 +187,21 @@
   </si>
   <si>
     <t>0805</t>
+  </si>
+  <si>
+    <t>murata</t>
+  </si>
+  <si>
+    <t>GRM32ER71J106KA12L</t>
+  </si>
+  <si>
+    <t>10uF input decoupling</t>
+  </si>
+  <si>
+    <t>GRM155R71H104KE14J</t>
+  </si>
+  <si>
+    <t>0.1uF for high frequency</t>
   </si>
 </sst>
 </file>
@@ -218,13 +227,6 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -267,6 +269,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFD8D5CF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -331,7 +339,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
@@ -346,39 +354,39 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -387,35 +395,35 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -785,53 +793,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="19.5" customHeight="1">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
-      <c r="D2" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
+      <c r="A2" s="28"/>
+      <c r="B2" s="28"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="29"/>
-      <c r="B3" s="29"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="28"/>
     </row>
     <row r="6" spans="1:9" ht="28.5" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -839,86 +834,104 @@
         <v>1</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" s="6">
         <v>4</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="12" t="s">
-        <v>13</v>
-      </c>
       <c r="F7" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" ht="40.799999999999997">
       <c r="A8" s="6">
         <v>2</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C8" s="16">
         <v>1</v>
       </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="18"/>
+      <c r="D8" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="29" t="s">
+        <v>32</v>
+      </c>
       <c r="F8" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" s="20"/>
+        <v>33</v>
+      </c>
+      <c r="G8" s="20">
+        <v>1210</v>
+      </c>
       <c r="H8" s="21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I8" s="22"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" ht="40.799999999999997">
       <c r="A9" s="6">
         <v>3</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" s="16">
         <v>1</v>
       </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
+      <c r="D9" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>34</v>
+      </c>
       <c r="F9" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="18"/>
+        <v>35</v>
+      </c>
+      <c r="G9" s="18">
+        <v>1005</v>
+      </c>
       <c r="H9" s="23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I9" s="23"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" ht="40.799999999999997">
       <c r="A10" s="6">
         <v>4</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" s="16">
         <v>1</v>
       </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
+      <c r="D10" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>34</v>
+      </c>
       <c r="F10" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="18"/>
+        <v>24</v>
+      </c>
+      <c r="G10" s="18">
+        <v>1005</v>
+      </c>
       <c r="H10" s="23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I10" s="23"/>
     </row>
@@ -927,7 +940,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="16">
         <v>1</v>
@@ -935,11 +948,11 @@
       <c r="D11" s="17"/>
       <c r="E11" s="17"/>
       <c r="F11" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G11" s="18"/>
       <c r="H11" s="23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I11" s="23"/>
     </row>
@@ -948,7 +961,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="16">
         <v>1</v>
@@ -956,7 +969,7 @@
       <c r="D12" s="17"/>
       <c r="E12" s="17"/>
       <c r="F12" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G12" s="24"/>
       <c r="H12" s="23"/>
@@ -967,7 +980,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" s="16">
         <v>1</v>
@@ -975,13 +988,13 @@
       <c r="D13" s="17"/>
       <c r="E13" s="17"/>
       <c r="F13" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I13" s="23"/>
     </row>
@@ -990,7 +1003,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14" s="16">
         <v>1</v>
@@ -998,13 +1011,13 @@
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
       <c r="F14" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I14" s="23"/>
     </row>
@@ -1013,7 +1026,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="16">
         <v>1</v>
@@ -1021,7 +1034,7 @@
       <c r="D15" s="25"/>
       <c r="E15" s="17"/>
       <c r="F15" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G15" s="24"/>
       <c r="H15" s="23"/>
@@ -1127,10 +1140,9 @@
       <c r="I26" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A24:I24"/>
     <mergeCell ref="A26:I26"/>
-    <mergeCell ref="D2:F4"/>
     <mergeCell ref="A2:B3"/>
   </mergeCells>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Bom.xlsx
+++ b/Bom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Victus\Desktop\AVIONIX-28\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE09176-F67B-4660-AE46-AB46F2812886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21AC9EA-F392-49EE-BD7F-4876EA7DF046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="948" windowWidth="21600" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
   <si>
     <t>Item #</t>
   </si>
@@ -202,6 +202,9 @@
   </si>
   <si>
     <t>0.1uF for high frequency</t>
+  </si>
+  <si>
+    <t>any</t>
   </si>
 </sst>
 </file>
@@ -413,6 +416,9 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -421,9 +427,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -793,12 +796,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="19.5" customHeight="1">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="29"/>
     </row>
     <row r="6" spans="1:9" ht="28.5" customHeight="1">
       <c r="A6" s="3" t="s">
@@ -862,12 +865,12 @@
         <v>13</v>
       </c>
       <c r="C8" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="26" t="s">
         <v>32</v>
       </c>
       <c r="F8" s="19" t="s">
@@ -894,7 +897,7 @@
       <c r="D9" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="26" t="s">
         <v>34</v>
       </c>
       <c r="F9" s="19" t="s">
@@ -921,7 +924,7 @@
       <c r="D10" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="26" t="s">
         <v>34</v>
       </c>
       <c r="F10" s="19" t="s">
@@ -945,7 +948,9 @@
       <c r="C11" s="16">
         <v>1</v>
       </c>
-      <c r="D11" s="17"/>
+      <c r="D11" s="17" t="s">
+        <v>31</v>
+      </c>
       <c r="E11" s="17"/>
       <c r="F11" s="19" t="s">
         <v>25</v>
@@ -966,7 +971,9 @@
       <c r="C12" s="16">
         <v>1</v>
       </c>
-      <c r="D12" s="17"/>
+      <c r="D12" s="17" t="s">
+        <v>31</v>
+      </c>
       <c r="E12" s="17"/>
       <c r="F12" s="19" t="s">
         <v>26</v>
@@ -985,7 +992,9 @@
       <c r="C13" s="16">
         <v>1</v>
       </c>
-      <c r="D13" s="17"/>
+      <c r="D13" s="17" t="s">
+        <v>36</v>
+      </c>
       <c r="E13" s="17"/>
       <c r="F13" s="19" t="s">
         <v>19</v>
@@ -1008,7 +1017,9 @@
       <c r="C14" s="16">
         <v>1</v>
       </c>
-      <c r="D14" s="17"/>
+      <c r="D14" s="17" t="s">
+        <v>36</v>
+      </c>
       <c r="E14" s="17"/>
       <c r="F14" s="15" t="s">
         <v>21</v>
@@ -1107,15 +1118,15 @@
       <c r="I21" s="9"/>
     </row>
     <row r="24" spans="1:9" ht="14.4">
-      <c r="A24" s="26"/>
-      <c r="B24" s="26"/>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="26"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
+      <c r="A24" s="27"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
     </row>
     <row r="25" spans="1:9" ht="14.4">
       <c r="A25" s="11"/>
@@ -1129,15 +1140,15 @@
       <c r="I25" s="11"/>
     </row>
     <row r="26" spans="1:9" s="2" customFormat="1" ht="14.4">
-      <c r="A26" s="27"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
+      <c r="A26" s="28"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Bom.xlsx
+++ b/Bom.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Victus\Desktop\AVIONIX-28\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F21AC9EA-F392-49EE-BD7F-4876EA7DF046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B6540E-CCAE-45C4-AB55-1260E36688F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="948" windowWidth="21600" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
   <si>
     <t>Item #</t>
   </si>
@@ -165,9 +165,6 @@
     <t xml:space="preserve">L1 </t>
   </si>
   <si>
-    <t>55uH</t>
-  </si>
-  <si>
     <t>0.1uF</t>
   </si>
   <si>
@@ -183,12 +180,6 @@
     <t>smd</t>
   </si>
   <si>
-    <t>1206</t>
-  </si>
-  <si>
-    <t>0805</t>
-  </si>
-  <si>
     <t>murata</t>
   </si>
   <si>
@@ -205,13 +196,58 @@
   </si>
   <si>
     <t>any</t>
+  </si>
+  <si>
+    <t>GRM32ER71E226ME15L</t>
+  </si>
+  <si>
+    <t>Nil</t>
+  </si>
+  <si>
+    <t>IFSC2020DEER560M01</t>
+  </si>
+  <si>
+    <t>Vishay</t>
+  </si>
+  <si>
+    <t>TCC0805COG750J500BT</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">any </t>
+  </si>
+  <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>TPS54202DDCT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ic for taping down 28v input to 5v </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOT -6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">smd </t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 each </t>
+  </si>
+  <si>
+    <t>56uH</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -278,6 +314,30 @@
     <font>
       <sz val="16"/>
       <color rgb="FFD8D5CF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFD8D5CF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="4" tint="-0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="4" tint="-0.249977111117893"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -347,7 +407,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -427,6 +487,26 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -849,7 +929,7 @@
         <v>12</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="13" t="s">
@@ -868,19 +948,17 @@
         <v>2</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="20">
-        <v>1210</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="G8" s="20"/>
       <c r="H8" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I8" s="22"/>
     </row>
@@ -895,19 +973,17 @@
         <v>1</v>
       </c>
       <c r="D9" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="26" t="s">
-        <v>34</v>
-      </c>
       <c r="F9" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="18">
-        <v>1005</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="G9" s="18"/>
       <c r="H9" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I9" s="23"/>
     </row>
@@ -922,46 +998,46 @@
         <v>1</v>
       </c>
       <c r="D10" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="26" t="s">
-        <v>34</v>
-      </c>
       <c r="F10" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="18">
-        <v>1005</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="G10" s="18"/>
       <c r="H10" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I10" s="23"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" ht="40.799999999999997">
       <c r="A11" s="6">
         <v>5</v>
       </c>
       <c r="B11" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="16">
-        <v>1</v>
+      <c r="C11" s="37" t="s">
+        <v>47</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="17"/>
+        <v>28</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>34</v>
+      </c>
       <c r="F11" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G11" s="18"/>
       <c r="H11" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I11" s="23"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" ht="40.799999999999997">
       <c r="A12" s="6">
         <v>6</v>
       </c>
@@ -972,11 +1048,13 @@
         <v>1</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" s="17"/>
+        <v>28</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="F12" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G12" s="24"/>
       <c r="H12" s="23"/>
@@ -993,17 +1071,17 @@
         <v>1</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="17"/>
+        <v>33</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>35</v>
+      </c>
       <c r="F13" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="24" t="s">
-        <v>29</v>
-      </c>
+      <c r="G13" s="24"/>
       <c r="H13" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I13" s="23"/>
     </row>
@@ -1018,17 +1096,17 @@
         <v>1</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E14" s="17"/>
+        <v>33</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>35</v>
+      </c>
       <c r="F14" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="24" t="s">
-        <v>30</v>
-      </c>
+      <c r="G14" s="24"/>
       <c r="H14" s="23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I14" s="23"/>
     </row>
@@ -1042,36 +1120,68 @@
       <c r="C15" s="16">
         <v>1</v>
       </c>
-      <c r="D15" s="25"/>
-      <c r="E15" s="17"/>
+      <c r="D15" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>36</v>
+      </c>
       <c r="F15" s="15" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="G15" s="24"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="31" t="s">
+        <v>27</v>
+      </c>
       <c r="I15" s="23"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="B16" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16" s="16">
+        <v>1</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="17">
+        <v>51</v>
+      </c>
       <c r="G16" s="24"/>
-      <c r="H16" s="20"/>
+      <c r="H16" s="21" t="s">
+        <v>27</v>
+      </c>
       <c r="I16" s="20"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
+      <c r="B17" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="33">
+        <v>1</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="I17" s="36"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>

--- a/Bom.xlsx
+++ b/Bom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Victus\Desktop\AVIONIX-28\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B6540E-CCAE-45C4-AB55-1260E36688F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34D930E-246F-48C0-8641-4A54060DAB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -407,7 +407,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -441,13 +441,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -476,9 +469,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -488,26 +478,49 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -876,15 +889,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="19.5" customHeight="1">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="29"/>
-      <c r="B3" s="29"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
     </row>
     <row r="6" spans="1:9" ht="28.5" customHeight="1">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="34" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -913,275 +926,279 @@
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6">
+      <c r="A7" s="28">
         <v>1</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="28">
         <v>4</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="13" t="s">
+      <c r="G7" s="40"/>
+      <c r="H7" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="9"/>
+      <c r="I7" s="42"/>
     </row>
     <row r="8" spans="1:9" ht="40.799999999999997">
-      <c r="A8" s="6">
+      <c r="A8" s="28">
         <v>2</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="13">
         <v>2</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="E8" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="20"/>
-      <c r="H8" s="21" t="s">
+      <c r="G8" s="17"/>
+      <c r="H8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="22"/>
+      <c r="I8" s="19"/>
     </row>
     <row r="9" spans="1:9" ht="40.799999999999997">
-      <c r="A9" s="6">
+      <c r="A9" s="28">
         <v>3</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="13">
         <v>1</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="E9" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="23" t="s">
+      <c r="G9" s="15"/>
+      <c r="H9" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="23"/>
+      <c r="I9" s="20"/>
     </row>
     <row r="10" spans="1:9" ht="40.799999999999997">
-      <c r="A10" s="6">
+      <c r="A10" s="28">
         <v>4</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="13">
         <v>1</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="E10" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="18"/>
-      <c r="H10" s="23" t="s">
+      <c r="G10" s="15"/>
+      <c r="H10" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="23"/>
+      <c r="I10" s="20"/>
     </row>
     <row r="11" spans="1:9" ht="40.799999999999997">
-      <c r="A11" s="6">
+      <c r="A11" s="28">
         <v>5</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="30" t="s">
+      <c r="E11" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="18"/>
-      <c r="H11" s="23" t="s">
+      <c r="G11" s="15"/>
+      <c r="H11" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="23"/>
+      <c r="I11" s="20"/>
     </row>
     <row r="12" spans="1:9" ht="40.799999999999997">
-      <c r="A12" s="6">
+      <c r="A12" s="28">
         <v>6</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="13">
         <v>1</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="30" t="s">
+      <c r="E12" s="37" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="24"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="23"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6">
+      <c r="A13" s="28">
         <v>7</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="13">
         <v>1</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="24"/>
-      <c r="H13" s="23" t="s">
+      <c r="G13" s="21"/>
+      <c r="H13" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="23"/>
+      <c r="I13" s="20"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6">
+      <c r="A14" s="28">
         <v>8</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="13">
         <v>1</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="24"/>
-      <c r="H14" s="23" t="s">
+      <c r="G14" s="21"/>
+      <c r="H14" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="I14" s="23"/>
+      <c r="I14" s="20"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6">
+      <c r="A15" s="28">
         <v>9</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="13">
         <v>1</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G15" s="24"/>
-      <c r="H15" s="31" t="s">
+      <c r="G15" s="21"/>
+      <c r="H15" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="23"/>
+      <c r="I15" s="20"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="15" t="s">
+      <c r="A16" s="28">
+        <v>10</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="13">
         <v>1</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="14">
         <v>51</v>
       </c>
-      <c r="G16" s="24"/>
-      <c r="H16" s="21" t="s">
+      <c r="G16" s="21"/>
+      <c r="H16" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="I16" s="20"/>
+      <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6"/>
-      <c r="B17" s="32" t="s">
+      <c r="A17" s="28">
+        <v>11</v>
+      </c>
+      <c r="B17" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="30">
         <v>1</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="E17" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="32" t="s">
+      <c r="F17" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="35" t="s">
+      <c r="G17" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="H17" s="36" t="s">
+      <c r="H17" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="I17" s="36"/>
+      <c r="I17" s="33"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -1228,15 +1245,15 @@
       <c r="I21" s="9"/>
     </row>
     <row r="24" spans="1:9" ht="14.4">
-      <c r="A24" s="27"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
     </row>
     <row r="25" spans="1:9" ht="14.4">
       <c r="A25" s="11"/>
@@ -1250,15 +1267,15 @@
       <c r="I25" s="11"/>
     </row>
     <row r="26" spans="1:9" s="2" customFormat="1" ht="14.4">
-      <c r="A26" s="28"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
+      <c r="A26" s="24"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Bom.xlsx
+++ b/Bom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Victus\Desktop\AVIONIX-28\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34D930E-246F-48C0-8641-4A54060DAB1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D8EF48-6CDC-4DCD-87F9-48CD953684C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="51">
   <si>
     <t>Item #</t>
   </si>
@@ -180,6 +180,9 @@
     <t>smd</t>
   </si>
   <si>
+    <t>0805</t>
+  </si>
+  <si>
     <t>murata</t>
   </si>
   <si>
@@ -204,9 +207,6 @@
     <t>Nil</t>
   </si>
   <si>
-    <t>IFSC2020DEER560M01</t>
-  </si>
-  <si>
     <t>Vishay</t>
   </si>
   <si>
@@ -219,9 +219,6 @@
     <t xml:space="preserve">any </t>
   </si>
   <si>
-    <t>TI</t>
-  </si>
-  <si>
     <t>TPS54202DDCT</t>
   </si>
   <si>
@@ -231,23 +228,32 @@
     <t xml:space="preserve">SOT -6 </t>
   </si>
   <si>
-    <t xml:space="preserve">smd </t>
-  </si>
-  <si>
     <t>U1</t>
   </si>
   <si>
     <t xml:space="preserve">1 each </t>
   </si>
   <si>
-    <t>56uH</t>
+    <t xml:space="preserve"> O4O2</t>
+  </si>
+  <si>
+    <t>O4O2</t>
+  </si>
+  <si>
+    <t>CD54NP-220MC</t>
+  </si>
+  <si>
+    <t>22uH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Texas </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,13 +336,20 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="10"/>
       <color theme="4" tint="-0.249977111117893"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="7"/>
+      <color rgb="FFBDB7AF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
       <color theme="4" tint="-0.249977111117893"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -407,7 +420,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -491,13 +504,10 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -521,6 +531,15 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -897,7 +916,7 @@
       <c r="B3" s="25"/>
     </row>
     <row r="6" spans="1:9" ht="28.5" customHeight="1">
-      <c r="A6" s="34" t="s">
+      <c r="A6" s="33" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -929,26 +948,26 @@
       <c r="A7" s="28">
         <v>1</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="37" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="28">
         <v>4</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="39" t="s">
+      <c r="F7" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="40"/>
-      <c r="H7" s="41" t="s">
+      <c r="G7" s="39"/>
+      <c r="H7" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="42"/>
+      <c r="I7" s="41"/>
     </row>
     <row r="8" spans="1:9" ht="40.799999999999997">
       <c r="A8" s="28">
@@ -961,15 +980,17 @@
         <v>2</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="36" t="s">
         <v>29</v>
       </c>
+      <c r="E8" s="35" t="s">
+        <v>30</v>
+      </c>
       <c r="F8" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="17"/>
+        <v>31</v>
+      </c>
+      <c r="G8" s="43">
+        <v>1210</v>
+      </c>
       <c r="H8" s="18" t="s">
         <v>27</v>
       </c>
@@ -986,15 +1007,17 @@
         <v>1</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="36" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>32</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="15"/>
+        <v>33</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>46</v>
+      </c>
       <c r="H9" s="20" t="s">
         <v>27</v>
       </c>
@@ -1011,15 +1034,17 @@
         <v>1</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="36" t="s">
-        <v>31</v>
+        <v>29</v>
+      </c>
+      <c r="E10" s="35" t="s">
+        <v>32</v>
       </c>
       <c r="F10" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="15"/>
+      <c r="G10" s="16" t="s">
+        <v>47</v>
+      </c>
       <c r="H10" s="20" t="s">
         <v>27</v>
       </c>
@@ -1033,18 +1058,20 @@
         <v>16</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="37" t="s">
-        <v>34</v>
+        <v>29</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>35</v>
       </c>
       <c r="F11" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="15"/>
+      <c r="G11" s="15">
+        <v>1210</v>
+      </c>
       <c r="H11" s="20" t="s">
         <v>27</v>
       </c>
@@ -1061,15 +1088,17 @@
         <v>1</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="36" t="s">
         <v>38</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="21"/>
+      <c r="G12" s="42" t="s">
+        <v>28</v>
+      </c>
       <c r="H12" s="20"/>
       <c r="I12" s="20"/>
     </row>
@@ -1084,15 +1113,17 @@
         <v>1</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F13" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="21"/>
+      <c r="G13" s="42" t="s">
+        <v>28</v>
+      </c>
       <c r="H13" s="20" t="s">
         <v>27</v>
       </c>
@@ -1109,15 +1140,17 @@
         <v>1</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="21"/>
+      <c r="G14" s="42" t="s">
+        <v>28</v>
+      </c>
       <c r="H14" s="20" t="s">
         <v>27</v>
       </c>
@@ -1136,11 +1169,11 @@
       <c r="D15" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="E15" s="14" t="s">
-        <v>36</v>
+      <c r="E15" s="12" t="s">
+        <v>48</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G15" s="21"/>
       <c r="H15" s="26" t="s">
@@ -1162,12 +1195,14 @@
         <v>40</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F16" s="14">
         <v>51</v>
       </c>
-      <c r="G16" s="21"/>
+      <c r="G16" s="42" t="s">
+        <v>28</v>
+      </c>
       <c r="H16" s="18" t="s">
         <v>27</v>
       </c>
@@ -1178,27 +1213,27 @@
         <v>11</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C17" s="30">
         <v>1</v>
       </c>
       <c r="D17" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="F17" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="29" t="s">
+      <c r="G17" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="H17" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="I17" s="33"/>
+      <c r="H17" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" s="32"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>

--- a/Bom.xlsx
+++ b/Bom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Victus\Desktop\AVIONIX-28\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D8EF48-6CDC-4DCD-87F9-48CD953684C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E7869E9-CFD8-447E-B77B-3ABD1BBF3329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -482,15 +483,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -539,6 +531,15 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -908,15 +909,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="19.5" customHeight="1">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
+      <c r="A3" s="44"/>
+      <c r="B3" s="44"/>
     </row>
     <row r="6" spans="1:9" ht="28.5" customHeight="1">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="30" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -945,32 +946,32 @@
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="28">
+      <c r="A7" s="25">
         <v>1</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="25">
         <v>4</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="34" t="s">
+      <c r="E7" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="39"/>
-      <c r="H7" s="40" t="s">
+      <c r="G7" s="36"/>
+      <c r="H7" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="41"/>
+      <c r="I7" s="38"/>
     </row>
     <row r="8" spans="1:9" ht="40.799999999999997">
-      <c r="A8" s="28">
+      <c r="A8" s="25">
         <v>2</v>
       </c>
       <c r="B8" s="12" t="s">
@@ -982,13 +983,13 @@
       <c r="D8" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="32" t="s">
         <v>30</v>
       </c>
       <c r="F8" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="43">
+      <c r="G8" s="40">
         <v>1210</v>
       </c>
       <c r="H8" s="18" t="s">
@@ -997,7 +998,7 @@
       <c r="I8" s="19"/>
     </row>
     <row r="9" spans="1:9" ht="40.799999999999997">
-      <c r="A9" s="28">
+      <c r="A9" s="25">
         <v>3</v>
       </c>
       <c r="B9" s="12" t="s">
@@ -1009,7 +1010,7 @@
       <c r="D9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="32" t="s">
         <v>32</v>
       </c>
       <c r="F9" s="16" t="s">
@@ -1024,7 +1025,7 @@
       <c r="I9" s="20"/>
     </row>
     <row r="10" spans="1:9" ht="40.799999999999997">
-      <c r="A10" s="28">
+      <c r="A10" s="25">
         <v>4</v>
       </c>
       <c r="B10" s="12" t="s">
@@ -1036,7 +1037,7 @@
       <c r="D10" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="32" t="s">
         <v>32</v>
       </c>
       <c r="F10" s="16" t="s">
@@ -1051,19 +1052,19 @@
       <c r="I10" s="20"/>
     </row>
     <row r="11" spans="1:9" ht="40.799999999999997">
-      <c r="A11" s="28">
+      <c r="A11" s="25">
         <v>5</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="24" t="s">
         <v>45</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="36" t="s">
+      <c r="E11" s="33" t="s">
         <v>35</v>
       </c>
       <c r="F11" s="16" t="s">
@@ -1078,7 +1079,7 @@
       <c r="I11" s="20"/>
     </row>
     <row r="12" spans="1:9" ht="40.799999999999997">
-      <c r="A12" s="28">
+      <c r="A12" s="25">
         <v>6</v>
       </c>
       <c r="B12" s="12" t="s">
@@ -1090,20 +1091,20 @@
       <c r="D12" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="36" t="s">
+      <c r="E12" s="33" t="s">
         <v>38</v>
       </c>
       <c r="F12" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="42" t="s">
+      <c r="G12" s="39" t="s">
         <v>28</v>
       </c>
       <c r="H12" s="20"/>
       <c r="I12" s="20"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="28">
+      <c r="A13" s="25">
         <v>7</v>
       </c>
       <c r="B13" s="12" t="s">
@@ -1121,7 +1122,7 @@
       <c r="F13" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="42" t="s">
+      <c r="G13" s="39" t="s">
         <v>28</v>
       </c>
       <c r="H13" s="20" t="s">
@@ -1130,7 +1131,7 @@
       <c r="I13" s="20"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="28">
+      <c r="A14" s="25">
         <v>8</v>
       </c>
       <c r="B14" s="12" t="s">
@@ -1148,7 +1149,7 @@
       <c r="F14" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="42" t="s">
+      <c r="G14" s="39" t="s">
         <v>28</v>
       </c>
       <c r="H14" s="20" t="s">
@@ -1157,7 +1158,7 @@
       <c r="I14" s="20"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="28">
+      <c r="A15" s="25">
         <v>9</v>
       </c>
       <c r="B15" s="12" t="s">
@@ -1176,13 +1177,13 @@
         <v>49</v>
       </c>
       <c r="G15" s="21"/>
-      <c r="H15" s="26" t="s">
+      <c r="H15" s="23" t="s">
         <v>27</v>
       </c>
       <c r="I15" s="20"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="28">
+      <c r="A16" s="25">
         <v>10</v>
       </c>
       <c r="B16" s="12" t="s">
@@ -1200,7 +1201,7 @@
       <c r="F16" s="14">
         <v>51</v>
       </c>
-      <c r="G16" s="42" t="s">
+      <c r="G16" s="39" t="s">
         <v>28</v>
       </c>
       <c r="H16" s="18" t="s">
@@ -1209,31 +1210,31 @@
       <c r="I16" s="17"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="28">
+      <c r="A17" s="25">
         <v>11</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="27">
         <v>1</v>
       </c>
-      <c r="D17" s="29" t="s">
+      <c r="D17" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="44" t="s">
+      <c r="E17" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="F17" s="29" t="s">
+      <c r="F17" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="G17" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="H17" s="32" t="s">
+      <c r="H17" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="I17" s="32"/>
+      <c r="I17" s="29"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -1280,15 +1281,15 @@
       <c r="I21" s="9"/>
     </row>
     <row r="24" spans="1:9" ht="14.4">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
+      <c r="A24" s="42"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
     </row>
     <row r="25" spans="1:9" ht="14.4">
       <c r="A25" s="11"/>
@@ -1302,15 +1303,15 @@
       <c r="I25" s="11"/>
     </row>
     <row r="26" spans="1:9" s="2" customFormat="1" ht="14.4">
-      <c r="A26" s="24"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
+      <c r="A26" s="43"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="43"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="3">
